--- a/Result/profitability/3611.xlsx
+++ b/Result/profitability/3611.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.51</v>
       </c>
       <c r="M2" t="n">
-        <v>3.83375</v>
+        <v>4.0875</v>
       </c>
       <c r="N2" t="n">
-        <v>31.97875</v>
+        <v>32.01625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.13</v>
       </c>
       <c r="M3" t="n">
-        <v>3.59</v>
+        <v>3.86875</v>
       </c>
       <c r="N3" t="n">
-        <v>32.03375</v>
+        <v>32.3325</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.49</v>
       </c>
       <c r="M4" t="n">
-        <v>3.41625</v>
+        <v>3.57125</v>
       </c>
       <c r="N4" t="n">
-        <v>32.83125</v>
+        <v>33.03375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.99</v>
       </c>
       <c r="M5" t="n">
-        <v>3.05625</v>
+        <v>3.09875</v>
       </c>
       <c r="N5" t="n">
-        <v>33.69125</v>
+        <v>33.4675</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7375</v>
+        <v>2.71875</v>
       </c>
       <c r="N6" t="n">
-        <v>34.28625</v>
+        <v>33.9925</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>2.24875</v>
+        <v>2.17</v>
       </c>
       <c r="N7" t="n">
-        <v>35.1025</v>
+        <v>34.95375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>1.735</v>
+        <v>1.80375</v>
       </c>
       <c r="N8" t="n">
-        <v>36.34125</v>
+        <v>36.0325</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3611</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3144</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2159</v>
+      </c>
+      <c r="E75" t="n">
+        <v>985</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>295</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>24</v>
+      </c>
+      <c r="J75" t="n">
+        <v>319</v>
+      </c>
+      <c r="K75" t="n">
+        <v>243</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>4.40875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>31.77625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5500000000000007</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1206140350877194</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.470000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0730553090801539</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3400000000000007</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.07127882599580726</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.790000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05402958044068829</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
